--- a/Assets/test260903/chapter0206.xlsx
+++ b/Assets/test260903/chapter0206.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="145" documentId="11_B8F2C21C3BF8F8042E83A027A8BF20349734E0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CBF73FA-AA24-4659-9344-B907F738064A}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0206" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0206" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>Command</t>
   </si>
@@ -66,37 +75,325 @@
     <t>WaitInput</t>
   </si>
   <si>
-    <t>BgOff</t>
-  </si>
-  <si>
     <t>Chapter2-6です</t>
   </si>
   <si>
+    <t>*chapter0301_Start</t>
+  </si>
+  <si>
     <t>Jump</t>
-  </si>
-  <si>
-    <t>*chapter0301_Start</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……街が遠ざかっていく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>主人公</t>
+    <rPh sb="0" eb="3">
+      <t>シュジンコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：プライベートジェットの機内</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>機内環境音</t>
+  </si>
+  <si>
+    <t>離れてしまえば、本当に小さな街だ。
+もう二度と来ないと思うけれど</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>自動操縦に切り替えたぞー。
+あとは着陸までは手放しでＯＫ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それにしても、
+まさかこんな形で上京するなんてね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喧嘩の勢いって、やっぱいいわ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>く～～ワクワクする！
+向こうには強いヤツがいるんだよね？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは瞳を輝かせている。
+だが……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>正直……美鈴さんより強い人なんて
+ちょっと想像がつかない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、アタシって強いうえに
+メチャクチャ運がいいよね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ずっと修羅場を探してた。
+そこにエロガキ、あんたが現れて……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おかげでイイ修羅場に出会えた。
+感謝しなくちゃね♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「僕は両親に殺されかけたんだぞ」
+……と、答えたい気持ちもある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし美鈴さんの屈託のない笑顔は、
+そんな些細なこと忘れさせてくれた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前ら……ほ、本気か？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父</t>
+  </si>
+  <si>
+    <t>弱気</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>東京なんて……
+死にに行くようなもんだぞ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父の、蚊の鳴くような声がした。
+その姿は酷く貧相に見える</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悪いことは言わねぇ。
+今からでも引き返すんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そして何もかも忘れて、
+どこか遠くへ逃げるんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そうすれば、父親もお前を追わない。
+解決するはずだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これ以上、事を大きくする必要はない。
+お前が消えさえすれば、何とでもなる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父の言っていることは分かる。
+それも一つの手だろう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だけど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ、どうする？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まぁ、ぶっちゃけアリだとは思うよ。
+このオッサンがいったパターンも</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、アタシはオススメしないかなぁ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だって売られた喧嘩から逃げたら、
+一生、おびえながら生きることになるし</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何よりムカついたまんまだ。
+それって、凄くムカつくよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒り</t>
+    <rPh sb="0" eb="1">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんな女の言葉に惑わされるな。
+逆だ、ここで復讐すれば……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お前は一生、苦しむぞ。
+復讐は何も生まない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父の言う通りだ。
+確かに復讐は何も生まない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だが……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殺されかけてガマンできるか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そういうこと♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あとオッサン、心配しなくていいよ。
+このエロガキはアタシが守るから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>無敵のアタシが守るということは、
+このエロガキも無敵ってことだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>つーわけで、ちょっと寝てな！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ぐけっ……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殴打</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Shake</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>x=3.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんが叔父をブン殴った</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +401,68 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +652,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1066"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,686 +711,1016 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-    </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-    </row>
-    <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
+    </row>
+    <row r="13" spans="1:12" ht="28.8" customHeight="1">
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="28.8" customHeight="1">
+      <c r="B14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.2" customHeight="1">
+      <c r="B15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
+      <c r="B18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="I18" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B19" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="I19" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="28.2" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
+      <c r="B20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1">
+      <c r="B21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.2" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
+      <c r="B23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.2" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
+      <c r="B24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B26" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B27" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="I27" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="B28" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="30" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B31" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="27" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="30" customHeight="1">
+      <c r="B35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B39" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B40" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="30" customHeight="1">
+      <c r="B41" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A42" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="I42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
+    <row r="44" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B44" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B48" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A49" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="6"/>
+      <c r="I49" s="9"/>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A50" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I50" s="9"/>
+    </row>
+    <row r="51" spans="1:10" ht="13.2" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
+      <c r="B51" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A52" s="1"/>
+      <c r="B52" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I52" s="9"/>
+    </row>
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="1"/>
+      <c r="B53" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
       <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
-      <c r="A55" s="1"/>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" ht="13.5" customHeight="1">
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
       <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
       <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
       <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" ht="13.5" customHeight="1">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" ht="13.5" customHeight="1">
+    <row r="61" spans="1:10" ht="13.5" customHeight="1">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" ht="13.5" customHeight="1">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
       <c r="I64" s="1"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
       <c r="I65" s="1"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1">
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
       <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
       <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="C69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" ht="13.5" customHeight="1">
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
+      <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" ht="13.5" customHeight="1">
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1">
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" ht="13.5" customHeight="1">
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" ht="13.5" customHeight="1">
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
+      <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" ht="13.5" customHeight="1">
+    <row r="78" spans="1:9" ht="13.5" customHeight="1">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" ht="13.5" customHeight="1">
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
       <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="I86" s="1"/>
-    </row>
-    <row r="87" ht="13.5" customHeight="1">
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
       <c r="I87" s="1"/>
     </row>
-    <row r="88" ht="13.5" customHeight="1">
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
       <c r="I88" s="1"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
+      <c r="B90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
       <c r="I91" s="1"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1">
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" ht="13.5" customHeight="1">
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
+      <c r="C95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" ht="13.5" customHeight="1">
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" ht="13.5" customHeight="1">
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" ht="13.5" customHeight="1">
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" ht="13.5" customHeight="1">
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="1"/>
+      <c r="B107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1"/>
+      <c r="H108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
+      <c r="C117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" ht="13.5" customHeight="1">
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" ht="13.5" customHeight="1">
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
       <c r="I121" s="1"/>
-    </row>
-    <row r="122" ht="13.5" customHeight="1">
+      <c r="J121" s="1"/>
+    </row>
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" ht="13.5" customHeight="1">
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+    </row>
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
       <c r="I123" s="1"/>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" ht="13.5" customHeight="1">
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" ht="13.5" customHeight="1">
+    </row>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
       <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
       <c r="I131" s="1"/>
-    </row>
-    <row r="132" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
+      <c r="J131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+      <c r="B134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+      <c r="B139" s="1"/>
+      <c r="H139" s="1"/>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="1"/>
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="149" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="161" ht="13.5" customHeight="1"/>
     <row r="162" ht="13.5" customHeight="1"/>
     <row r="163" ht="13.5" customHeight="1"/>
@@ -1107,22 +1753,29 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" ht="13.5" customHeight="1"/>
-    <row r="194" ht="13.5" customHeight="1"/>
-    <row r="195" ht="13.5" customHeight="1"/>
-    <row r="196" ht="13.5" customHeight="1"/>
-    <row r="197" ht="13.5" customHeight="1"/>
-    <row r="198" ht="13.5" customHeight="1"/>
-    <row r="199" ht="13.5" customHeight="1"/>
-    <row r="200" ht="13.5" customHeight="1"/>
-    <row r="201" ht="13.5" customHeight="1"/>
-    <row r="202" ht="13.5" customHeight="1"/>
-    <row r="203" ht="13.5" customHeight="1"/>
-    <row r="204" ht="13.5" customHeight="1"/>
-    <row r="205" ht="13.5" customHeight="1"/>
-    <row r="206" ht="13.5" customHeight="1"/>
-    <row r="207" ht="13.5" customHeight="1"/>
-    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="203" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="204" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A204" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="206" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="209" ht="13.5" customHeight="1"/>
     <row r="210" ht="13.5" customHeight="1"/>
     <row r="211" ht="13.5" customHeight="1"/>
@@ -1973,10 +2626,17 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0206.xlsx
+++ b/Assets/test260903/chapter0206.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="11_B8F2C21C3BF8F8042E83A027A8BF20349734E0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CBF73FA-AA24-4659-9344-B907F738064A}"/>
+  <xr:revisionPtr revIDLastSave="459" documentId="11_B8F2C21C3BF8F8042E83A027A8BF20349734E0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A092DDD-265C-4199-A99F-FF3A08E71C44}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="172">
   <si>
     <t>Command</t>
   </si>
@@ -346,6 +346,452 @@
   </si>
   <si>
     <t>美鈴さんが叔父をブン殴った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>白目をむいて失神している。
+このまま東京まで眠っておいてもらおう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>さて……ちょい寝るね。
+エロガキも眠った方がいいよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>体力をためとかなきゃ。
+東京に着いたら、またバタバタだよ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>たぶんスゲー強いやつが、
+ガンガンに襲ってくるんだよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>考えただけでテンション上がるね！
+あははは、上等上等っ♪</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんの言う通りだ。
+少し眠っておこう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>色々あって疲れた。
+銃撃戦に、カーチェイスに……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>両親に裏切られて、
+殺されかけて……散々な1日だった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だが……一つだけ幸運なことがあった。
+美鈴さんに出会えたことだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おやすみ～～</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんがいなければ、
+僕はとっくに殺されていただろう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それが、こうして生きている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>きっとこれから、
+さらに過酷な戦いが待っているはずだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、美鈴さんと一緒なら、
+絶対に何とかなるだろう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>がっ……ぐ～～～ぐ～～Zzzzz</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>目閉じ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>礼をいうべきだろう。
+美鈴さんに、出会えたことに</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ありがとう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>がっ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>コラ！　人が寝てるのを邪魔すんな！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イテ！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何で殴るんですか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人が寝てるのに、
+急に声をかけるからだよ！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>睡眠の邪魔はよくねーぞ！
+アタシじゃなくてもキレる！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>せっかく、お礼を言ったのに……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あ～？　お礼？
+そんなん必要ないって</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>照れ</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシは売られたケンカを買っただけ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>元からケンカしたかったし……
+ある意味、ちょうど良かったかな</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何にも感謝されるようなことは、
+してないし</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>むしろね、アタシみたいな人間に、
+感謝なんてしてたら後悔するよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悲しみ</t>
+    <rPh sb="0" eb="1">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシはムカつくやつを
+ブッ殺してるだけだからさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そんなことはないと思う。
+僕は知っている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父も、父も、白蛇の男も、
+僕を殺そうとした</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕を殺した方が利益があるからだ。
+でも、美鈴さんは違った</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あの時……
+ロシア人の殺し屋と話していた時……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopSe</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：街中</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（お前はガキを殺せって頼まれたから、
+殺そうとした、それだけってわけだ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（つまり、お前は命令さえあれば、
+ガキでも殺す男なんだな？）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（そんなクソ汚れを、
+野放しにしておくことはできるか？）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（じゃあな）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（受ける仕事は選ぶべきだったな。
+じゃないと、今日みたいに地雷を踏む）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（子どもを子ども扱いしない輩が、
+アタシは世界で一番嫌いなんだよ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは損得抜きに、
+「子供を殺すこと」を禁じている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bg</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そういう「美学」を持っている人間は、
+何よりも信頼できる。だから……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さん、これからもよろしく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ん？　ああ、そりゃね。
+こっちこそよろしく</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕も子供は殺しません</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>約束しますよ。美鈴さん</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そりゃイイことだけど……
+何でまた、急にどうしたの？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんの敵になりたくない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ん？　もしかして……
+あんた、あの時の話を理解してたの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-7-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ロシア語はできます</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>マジか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ、ロシア語が分かるの？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-8-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これでも経営者の卵ですから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ハハハハ、言うね～！
+アタシ、いい客と出会えたのかも</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキと出会って、えっと……
+まだ5時間しか経ってない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、今まで警護した、
+どの客よりも楽しいし、イイ客だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>まぁ、物思いに耽ることが多くて、
+めんどくせぇとは思うけど……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>敵が多くて楽しいし、
+思ったより優秀っぽい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あんたが「子供は殺さない」って
+約束をしてくれるなら……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ、改めて約束してあげよー！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あんたがアタシをムカつかせない限り、
+アタシはあんたを守ってやる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキの味方になって、
+ケンカ売ってくるヤツは全員倒す</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……約束するよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0206-10-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>よろしくお願いします</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>うっし、じゃあ一緒に寝よう。
+まだまだ戦いは続くからさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんはまた眠りについた。
+僕も、その隣に座る。そして……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>目閉じ</t>
+    <rPh sb="0" eb="1">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんの寝顔を見た。
+なんて安らかな寝顔なんだろう</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BgEvent</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>一枚絵：美鈴の寝顔</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>見ているだけで、僕も安心してくる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>少年を取り巻く課題は増えた。
+状況は、人生で最悪だといっていい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>考えることはたくさんある
+しかし、行きの飛行機とは正反対に……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>少年の意識は静かに遠のいていった。
+もちろん単純な肉体の疲労もあるが……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>絶対の安心と覚悟があったからだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>やがて少年は、
+束の間の平穏な眠りについた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BgEventOff</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（「オレは依頼されただけ」か。
+なるほど、なるほど……）</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -416,7 +862,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -439,6 +885,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -659,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1066"/>
+  <dimension ref="A1:L1081"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1284,459 +1733,1094 @@
         <v>75</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+    <row r="54" spans="1:10" ht="28.2" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="B54" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="I56" s="1"/>
+    <row r="55" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="I57" s="1"/>
+    <row r="57" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+    <row r="58" spans="1:10" ht="28.2" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
+      <c r="B58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+    <row r="59" spans="1:10" ht="30" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="I59" s="1"/>
+      <c r="B59" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="B60" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
+      <c r="I60" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B61" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I61" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="28.8" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="I62" s="1"/>
+      <c r="B62" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="B63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I65" s="1"/>
+    <row r="65" spans="1:9" ht="30" customHeight="1">
+      <c r="B65" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="66" spans="1:9" ht="13.5" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B66" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="30" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B68" s="1"/>
+      <c r="B67" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B68" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="I68" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="69" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
+      <c r="B69" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B70" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
+      <c r="I70" s="9" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
+      <c r="A71" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
+      <c r="I71" s="9" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="72" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A72" s="1"/>
+      <c r="A72" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="B72" s="1"/>
       <c r="I72" s="1"/>
     </row>
     <row r="73" spans="1:9" ht="13.5" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
+      <c r="B73" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
+      <c r="I73" s="9" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="74" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="A74" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74" s="5"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="9"/>
     </row>
     <row r="75" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
+      <c r="A75" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
+      <c r="D75" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="1"/>
+      <c r="I75" s="9"/>
     </row>
     <row r="76" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="I76" s="1"/>
+      <c r="B76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="77" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
+      <c r="B77" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="I77" s="1" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="78" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-    </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="A78" s="1"/>
+      <c r="B78" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H79" s="1"/>
+      <c r="I79" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B81" s="1"/>
+      <c r="B81" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="C81" s="1"/>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="I82" s="1"/>
+      <c r="I81" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="30" customHeight="1">
+      <c r="B82" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
+      <c r="B83" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B84" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1">
+      <c r="B85" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="30" customHeight="1">
+      <c r="B87" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B88" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="I88" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B89" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="30" customHeight="1">
+      <c r="B90" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B91" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I92" s="9"/>
+    </row>
+    <row r="93" spans="1:10" ht="27.6" customHeight="1">
+      <c r="C93" s="6"/>
+      <c r="I93" s="9"/>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
+      <c r="A94" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
       <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
+      <c r="A95" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A97" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1">
       <c r="A98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
+      <c r="B98" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D98" s="5"/>
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A99" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+    <row r="100" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B101" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D101" s="6"/>
+      <c r="I101" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B102" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D102" s="6"/>
+      <c r="I102" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="30.6" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="1"/>
-    </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="I109" s="1"/>
-    </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="I110" s="1"/>
-    </row>
-    <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="I118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B103" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D103" s="6"/>
+      <c r="I103" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A104" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="I104" s="11"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A105" s="1"/>
+      <c r="B105" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="30" customHeight="1">
+      <c r="B106" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B107" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A108" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="10">
+        <v>1</v>
+      </c>
+      <c r="I108" s="9"/>
+    </row>
+    <row r="109" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A109" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I109" s="9"/>
+    </row>
+    <row r="110" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A110" s="7"/>
+      <c r="B110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I110" s="9"/>
+    </row>
+    <row r="111" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A111" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C111" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111" s="9"/>
+    </row>
+    <row r="112" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A112" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G112" s="10">
+        <v>1</v>
+      </c>
+      <c r="I112" s="9"/>
+    </row>
+    <row r="113" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B113" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="1"/>
+      <c r="I113" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B114" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C114" s="1"/>
+      <c r="I114" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A115" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B117" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A118" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A119" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="I120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
+    <row r="120" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
+      <c r="B120" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A121" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="I121" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A122" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
       <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
-    </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="I127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+    </row>
+    <row r="123" spans="1:9" ht="27" customHeight="1">
+      <c r="B123" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A124" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A125" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B126" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A127" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
     <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="I129" s="1"/>
+      <c r="B129" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
+      <c r="B130" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
+      <c r="A131" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C131" s="1"/>
+      <c r="I131" s="1" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="132" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A132" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+    <row r="133" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A133" s="1"/>
+      <c r="B133" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="28.2" customHeight="1">
       <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B134" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="28.8" customHeight="1">
       <c r="A135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B135" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B136" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="27" customHeight="1">
       <c r="A137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B137" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I137" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="28.8" customHeight="1">
       <c r="A138" s="1"/>
+      <c r="B138" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I138" s="11" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="139" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A140" s="1"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
-    </row>
-    <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I141" s="1"/>
+      <c r="B139" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I139" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B140" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B141" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I142" s="1"/>
+      <c r="A142" s="1"/>
+      <c r="B142" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I143" s="1"/>
+      <c r="A143" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J143" s="1"/>
     </row>
     <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A144" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
       <c r="I144" s="1"/>
     </row>
-    <row r="145" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I146" s="1"/>
-    </row>
-    <row r="147" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I147" s="1"/>
-    </row>
-    <row r="148" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="149" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="150" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="151" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="152" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="153" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="154" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="155" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="156" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="157" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="158" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="159" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="160" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="145" spans="1:9" ht="30" customHeight="1">
+      <c r="B145" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="30" customHeight="1">
+      <c r="B146" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I146" s="9"/>
+    </row>
+    <row r="147" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A147" s="1"/>
+      <c r="B147" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A148" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="I148" s="11"/>
+    </row>
+    <row r="149" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A149" s="1"/>
+      <c r="B149" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B150" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I150" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A151" s="1"/>
+      <c r="I151" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A152" s="1"/>
+      <c r="I152" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A153" s="1"/>
+      <c r="B153" s="1"/>
+      <c r="H153" s="1"/>
+      <c r="I153" s="9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A154" s="1"/>
+      <c r="H154" s="1"/>
+      <c r="I154" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="28.2" customHeight="1">
+      <c r="I155" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A156" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156">
+        <v>1</v>
+      </c>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A157" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B157" s="7"/>
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A158" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="9:9" ht="13.5" customHeight="1">
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="164" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="165" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="166" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="167" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="168" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="169" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="170" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="171" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="172" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="173" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="9:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="9:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -1753,45 +2837,45 @@
     <row r="190" ht="13.5" customHeight="1"/>
     <row r="191" ht="13.5" customHeight="1"/>
     <row r="192" ht="13.5" customHeight="1"/>
-    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="199" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="203" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="204" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A204" s="1" t="s">
+    <row r="193" ht="13.5" customHeight="1"/>
+    <row r="194" ht="13.5" customHeight="1"/>
+    <row r="195" ht="13.5" customHeight="1"/>
+    <row r="196" ht="13.5" customHeight="1"/>
+    <row r="197" ht="13.5" customHeight="1"/>
+    <row r="198" ht="13.5" customHeight="1"/>
+    <row r="199" ht="13.5" customHeight="1"/>
+    <row r="200" ht="13.5" customHeight="1"/>
+    <row r="201" ht="13.5" customHeight="1"/>
+    <row r="202" ht="13.5" customHeight="1"/>
+    <row r="203" ht="13.5" customHeight="1"/>
+    <row r="204" ht="13.5" customHeight="1"/>
+    <row r="205" ht="13.5" customHeight="1"/>
+    <row r="206" ht="13.5" customHeight="1"/>
+    <row r="207" ht="13.5" customHeight="1"/>
+    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="209" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="210" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="211" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="219" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A219" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B204" s="1" t="s">
+      <c r="B219" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="206" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="209" ht="13.5" customHeight="1"/>
-    <row r="210" ht="13.5" customHeight="1"/>
-    <row r="211" ht="13.5" customHeight="1"/>
-    <row r="212" ht="13.5" customHeight="1"/>
-    <row r="213" ht="13.5" customHeight="1"/>
-    <row r="214" ht="13.5" customHeight="1"/>
-    <row r="215" ht="13.5" customHeight="1"/>
-    <row r="216" ht="13.5" customHeight="1"/>
-    <row r="217" ht="13.5" customHeight="1"/>
-    <row r="218" ht="13.5" customHeight="1"/>
-    <row r="219" ht="13.5" customHeight="1"/>
-    <row r="220" ht="13.5" customHeight="1"/>
-    <row r="221" ht="13.5" customHeight="1"/>
-    <row r="222" ht="13.5" customHeight="1"/>
-    <row r="223" ht="13.5" customHeight="1"/>
-    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="225" ht="13.5" customHeight="1"/>
     <row r="226" ht="13.5" customHeight="1"/>
     <row r="227" ht="13.5" customHeight="1"/>
@@ -2634,6 +3718,21 @@
     <row r="1064" ht="13.5" customHeight="1"/>
     <row r="1065" ht="13.5" customHeight="1"/>
     <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
+    <row r="1071" ht="13.5" customHeight="1"/>
+    <row r="1072" ht="13.5" customHeight="1"/>
+    <row r="1073" ht="13.5" customHeight="1"/>
+    <row r="1074" ht="13.5" customHeight="1"/>
+    <row r="1075" ht="13.5" customHeight="1"/>
+    <row r="1076" ht="13.5" customHeight="1"/>
+    <row r="1077" ht="13.5" customHeight="1"/>
+    <row r="1078" ht="13.5" customHeight="1"/>
+    <row r="1079" ht="13.5" customHeight="1"/>
+    <row r="1080" ht="13.5" customHeight="1"/>
+    <row r="1081" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0206.xlsx
+++ b/Assets/test260903/chapter0206.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="459" documentId="11_B8F2C21C3BF8F8042E83A027A8BF20349734E0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A092DDD-265C-4199-A99F-FF3A08E71C44}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="11_B8F2C21C3BF8F8042E83A027A8BF20349734E0BE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99E3D037-EA73-4C50-9915-BDAC2458AE78}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chapter0206" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="179">
   <si>
     <t>Command</t>
   </si>
@@ -792,6 +792,32 @@
   <si>
     <t>（「オレは依頼されただけ」か。
 なるほど、なるほど……）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_しんみり</t>
+  </si>
+  <si>
+    <t>BGM_しんみり</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_日常コミカル</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_決意</t>
+  </si>
+  <si>
+    <t>BGM_決意</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1108,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1081"/>
+  <dimension ref="A1:L1093"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1179,148 +1205,151 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="4">
-        <v>3</v>
-      </c>
+      <c r="H5" s="3"/>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="1"/>
+      <c r="A7" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:12" ht="13.5" customHeight="1">
       <c r="B8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
+      <c r="B9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
+      <c r="A10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>24</v>
+      <c r="A11" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="6" t="b">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:12" ht="13.5" customHeight="1">
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1" t="s">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="28.8" customHeight="1">
-      <c r="B13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="28.8" customHeight="1">
       <c r="B14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="28.2" customHeight="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28.8" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="B15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="13.5" customHeight="1">
+        <v>175</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" ht="28.8" customHeight="1">
       <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
@@ -1328,7 +1357,7 @@
         <v>29</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="28.2" customHeight="1">
@@ -1339,55 +1368,52 @@
         <v>29</v>
       </c>
       <c r="I17" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="1"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="I18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="I19" s="9" t="s">
-        <v>34</v>
-      </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" ht="28.2" customHeight="1">
+    <row r="20" spans="1:10" ht="30" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="I20" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="30" customHeight="1">
+      <c r="A21" s="1"/>
       <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C21" s="1"/>
       <c r="I21" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J21" s="1"/>
     </row>
@@ -1400,75 +1426,73 @@
         <v>29</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A23" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1">
       <c r="B23" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>38</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="28.2" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I25" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B26" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B27" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1"/>
-      <c r="I27" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1">
+    <row r="27" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="10" t="s">
+      <c r="B28" t="s">
         <v>42</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="H28" s="1"/>
       <c r="I28" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1">
-      <c r="A29" s="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="28.8" customHeight="1">
       <c r="B29" s="10" t="s">
         <v>42</v>
       </c>
@@ -1476,22 +1500,20 @@
         <v>43</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B30" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>43</v>
-      </c>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="1"/>
       <c r="I30" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="28.8" customHeight="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1">
+      <c r="A31" s="1"/>
       <c r="B31" s="10" t="s">
         <v>42</v>
       </c>
@@ -1499,63 +1521,66 @@
         <v>43</v>
       </c>
       <c r="I31" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="1:10" ht="30" customHeight="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B33" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B34" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="27" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="6" t="s">
+    <row r="35" spans="1:10" ht="27" customHeight="1">
+      <c r="A35" s="1"/>
+      <c r="B35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="6" t="s">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="1"/>
+      <c r="B36" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I33" s="9" t="s">
+      <c r="I36" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B34" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1">
-      <c r="B35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B36" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="28.2" customHeight="1">
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
       <c r="B37" s="6" t="s">
         <v>28</v>
       </c>
@@ -1563,893 +1588,896 @@
         <v>53</v>
       </c>
       <c r="I37" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1">
+      <c r="B38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="31.2" customHeight="1">
-      <c r="B38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="6" t="s">
+    <row r="41" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I38" s="9" t="s">
+      <c r="I41" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B39" s="10" t="s">
+    <row r="42" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B42" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I42" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B40" s="10" t="s">
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B43" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I43" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1">
-      <c r="B41" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A42" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="I42" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" ht="13.5" customHeight="1">
+    <row r="44" spans="1:10" ht="30" customHeight="1">
       <c r="B44" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B45" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A45" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="1"/>
       <c r="I45" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B46" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="31.2" customHeight="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A47" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="B47" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>68</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" customHeight="1">
       <c r="B48" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C48" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B49" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I49" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A49" s="8" t="s">
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="6"/>
-      <c r="I49" s="9"/>
-    </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A50" s="6" t="s">
+      <c r="C53" s="6"/>
+      <c r="I53" s="9"/>
+    </row>
+    <row r="54" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A54" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B54" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="6" t="s">
+      <c r="C54" s="1"/>
+      <c r="D54" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I50" s="9"/>
-    </row>
-    <row r="51" spans="1:10" ht="13.2" customHeight="1">
-      <c r="A51" s="1"/>
-      <c r="B51" s="10" t="s">
+      <c r="I54" s="9"/>
+    </row>
+    <row r="55" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A55" s="1"/>
+      <c r="B55" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I55" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="13.2" customHeight="1">
-      <c r="A52" s="1"/>
-      <c r="B52" s="10" t="s">
+    <row r="56" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C56" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I52" s="9"/>
-    </row>
-    <row r="53" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A53" s="1"/>
-      <c r="B53" s="6" t="s">
+      <c r="I56" s="9"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A57" s="1"/>
+      <c r="B57" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="9" t="s">
+      <c r="I57" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B55" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B56" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B57" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="28.2" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="30" customHeight="1">
-      <c r="A59" s="1"/>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A59" s="6" t="s">
+        <v>172</v>
+      </c>
       <c r="B59" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>81</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="I59" s="9"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
+    <row r="60" spans="1:10" ht="28.2" customHeight="1">
       <c r="B60" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I60" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="28.2" customHeight="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.8" customHeight="1">
       <c r="B61" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C61" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I61" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A62" s="1"/>
+        <v>78</v>
+      </c>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10" ht="27.6" customHeight="1">
       <c r="B62" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+        <v>79</v>
+      </c>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10" ht="28.2" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="7" t="s">
-        <v>53</v>
+      <c r="C63" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10" ht="30" customHeight="1">
+      <c r="A64" s="1"/>
       <c r="B64" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I64" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="30" customHeight="1">
       <c r="B65" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="C65" s="1"/>
       <c r="I65" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A66" s="1"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="28.2" customHeight="1">
       <c r="B66" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="C66" s="1"/>
       <c r="I66" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="30" customHeight="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28.8" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="27.6" customHeight="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="1"/>
       <c r="B68" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I68" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="13.5" customHeight="1">
       <c r="B69" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I69" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="28.2" customHeight="1">
+      <c r="C69" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" ht="30" customHeight="1">
       <c r="B70" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="1"/>
       <c r="I70" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A71" s="1"/>
+      <c r="B71" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="30" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="27.6" customHeight="1">
+      <c r="B73" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="I73" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="I75" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="5" t="s">
+    <row r="76" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A76" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="I71" s="9" t="s">
+      <c r="C76" s="1"/>
+      <c r="I76" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A72" s="1" t="s">
+    <row r="77" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A77" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A73" s="1"/>
-      <c r="B73" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H73" s="1"/>
-      <c r="I73" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A74" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C74" s="5"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="9"/>
-    </row>
-    <row r="75" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A75" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H75" s="1"/>
-      <c r="I75" s="9"/>
-    </row>
-    <row r="76" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B76" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B77" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="I77" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="B77" s="1"/>
+      <c r="I77" s="1"/>
     </row>
     <row r="78" spans="1:9" ht="13.5" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H78" s="1"/>
       <c r="I78" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A79" s="1"/>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A79" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="B79" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C79" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="9"/>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H80" s="1"/>
+      <c r="I80" s="9"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="6"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="9"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B82" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H79" s="1"/>
-      <c r="I79" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="27.6" customHeight="1">
-      <c r="B80" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I80" s="9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B81" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="I81" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="30" customHeight="1">
-      <c r="B82" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="I82" s="9" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="B83" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C83" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="I83" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="1"/>
+      <c r="B84" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A85" s="1"/>
+      <c r="B85" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H85" s="1"/>
+      <c r="I85" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B86" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B87" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="I87" s="9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="30" customHeight="1">
+      <c r="B88" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I83" s="9" t="s">
+      <c r="I88" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B89" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="I89" s="9" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B84" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" s="7" t="s">
+    <row r="90" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B90" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I84" s="9" t="s">
+      <c r="I90" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1">
-      <c r="B85" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C85" s="7" t="s">
+    <row r="91" spans="1:10" ht="30" customHeight="1">
+      <c r="B91" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I85" s="9" t="s">
+      <c r="I91" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B86" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C86" s="7" t="s">
+    <row r="92" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I86" s="9" t="s">
+      <c r="I92" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="30" customHeight="1">
-      <c r="B87" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C87" s="7" t="s">
+    <row r="93" spans="1:10" ht="30" customHeight="1">
+      <c r="B93" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I87" s="9" t="s">
+      <c r="I93" s="9" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B88" s="6" t="s">
+    <row r="94" spans="1:10" ht="30" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C94" s="7"/>
+      <c r="I94" s="9"/>
+    </row>
+    <row r="95" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B95" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C88" s="1"/>
-      <c r="I88" s="9" t="s">
+      <c r="C95" s="1"/>
+      <c r="I95" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B89" s="6" t="s">
+      <c r="J95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B96" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I89" s="9" t="s">
+      <c r="I96" s="9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="30" customHeight="1">
-      <c r="B90" s="6" t="s">
+    <row r="97" spans="1:10" ht="30" customHeight="1">
+      <c r="B97" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I90" s="9" t="s">
+      <c r="I97" s="9" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B91" s="6" t="s">
+    <row r="98" spans="1:10" ht="30" customHeight="1">
+      <c r="A98" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="6"/>
+      <c r="I98" s="9"/>
+    </row>
+    <row r="99" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B99" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I91" s="9" t="s">
+      <c r="I99" s="9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="27.6" customHeight="1">
-      <c r="I92" s="9"/>
-    </row>
-    <row r="93" spans="1:10" ht="27.6" customHeight="1">
-      <c r="C93" s="6"/>
-      <c r="I93" s="9"/>
-    </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="7" t="s">
+    <row r="100" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I100" s="9"/>
+    </row>
+    <row r="101" spans="1:10" ht="27.6" customHeight="1">
+      <c r="C101" s="6"/>
+      <c r="I101" s="9"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A102" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B102" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G94">
+      <c r="G102">
         <v>1</v>
       </c>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="6" t="s">
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A103" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B103" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="7"/>
-      <c r="B96" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C96" s="6" t="s">
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A104" s="7"/>
+      <c r="B104" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-    </row>
-    <row r="97" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A97" s="3" t="s">
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+    </row>
+    <row r="105" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A105" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B105" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-    </row>
-    <row r="98" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A98" s="1"/>
-      <c r="B98" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C98" s="5" t="s">
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+    </row>
+    <row r="106" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A106" s="1"/>
+      <c r="B106" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D98" s="5"/>
-    </row>
-    <row r="99" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A99" s="6" t="s">
+      <c r="D106" s="5"/>
+    </row>
+    <row r="107" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A107" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B107" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G99">
+      <c r="G107">
         <v>1</v>
       </c>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C100" s="6" t="s">
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I100" s="9" t="s">
+      <c r="I108" s="9" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B101" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C101" s="6" t="s">
+    <row r="109" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B109" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D101" s="6"/>
-      <c r="I101" s="9" t="s">
+      <c r="D109" s="6"/>
+      <c r="I109" s="9" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B102" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C102" s="6" t="s">
+    <row r="110" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B110" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D102" s="6"/>
-      <c r="I102" s="9" t="s">
+      <c r="D110" s="6"/>
+      <c r="I110" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A103" s="1"/>
-      <c r="B103" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C103" s="6" t="s">
+    <row r="111" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A111" s="1"/>
+      <c r="B111" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D103" s="6"/>
-      <c r="I103" s="11" t="s">
+      <c r="D111" s="6"/>
+      <c r="I111" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A104" s="8" t="s">
+    <row r="112" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A112" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B112" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="I104" s="11"/>
-    </row>
-    <row r="105" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A105" s="1"/>
-      <c r="B105" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C105" s="6" t="s">
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="I112" s="11"/>
+    </row>
+    <row r="113" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A113" s="1"/>
+      <c r="B113" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I105" s="11" t="s">
+      <c r="I113" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="30" customHeight="1">
-      <c r="B106" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C106" s="6" t="s">
+    <row r="114" spans="1:9" ht="30" customHeight="1">
+      <c r="B114" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I106" s="9" t="s">
+      <c r="I114" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B107" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C107" s="6" t="s">
+    <row r="115" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B115" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="I107" s="9" t="s">
+      <c r="I115" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A108" s="7" t="s">
+    <row r="116" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A116" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B116" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G108" s="10">
+      <c r="G116" s="10">
         <v>1</v>
       </c>
-      <c r="I108" s="9"/>
-    </row>
-    <row r="109" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A109" s="7" t="s">
+      <c r="I116" s="9"/>
+    </row>
+    <row r="117" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A117" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B117" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I109" s="9"/>
-    </row>
-    <row r="110" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A110" s="7"/>
-      <c r="B110" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C110" s="6" t="s">
+      <c r="I117" s="9"/>
+    </row>
+    <row r="118" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A118" s="7"/>
+      <c r="B118" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I110" s="9"/>
-    </row>
-    <row r="111" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A111" s="8" t="s">
+      <c r="I118" s="9"/>
+    </row>
+    <row r="119" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A119" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B119" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C111" s="6" t="b">
+      <c r="C119" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="I111" s="9"/>
-    </row>
-    <row r="112" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A112" s="6" t="s">
+      <c r="I119" s="9"/>
+    </row>
+    <row r="120" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A120" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B120" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G112" s="10">
+      <c r="G120" s="10">
         <v>1</v>
       </c>
-      <c r="I112" s="9"/>
-    </row>
-    <row r="113" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B113" s="6" t="s">
+      <c r="I120" s="9"/>
+    </row>
+    <row r="121" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A121" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G121" s="10"/>
+      <c r="I121" s="9"/>
+    </row>
+    <row r="122" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B122" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C113" s="1"/>
-      <c r="I113" s="9" t="s">
+      <c r="C122" s="1"/>
+      <c r="I122" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B114" s="6" t="s">
+    <row r="123" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B123" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C114" s="1"/>
-      <c r="I114" s="9" t="s">
+      <c r="C123" s="1"/>
+      <c r="I123" s="9" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A115" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I115" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A116" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="28.2" customHeight="1">
-      <c r="B117" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I117" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A118" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I118" s="9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A119" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B119" s="1"/>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A120" s="1"/>
-      <c r="B120" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A121" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A122" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="I122" s="1"/>
-    </row>
-    <row r="123" spans="1:9" ht="27" customHeight="1">
-      <c r="B123" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I123" s="9" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="13.5" customHeight="1">
@@ -2457,19 +2485,18 @@
         <v>62</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="13.5" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" spans="1:9" ht="28.8" customHeight="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="28.2" customHeight="1">
       <c r="B126" s="6" t="s">
         <v>28</v>
       </c>
@@ -2477,7 +2504,7 @@
         <v>53</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="13.5" customHeight="1">
@@ -2485,202 +2512,190 @@
         <v>62</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="13.5" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
       <c r="I128" s="1"/>
     </row>
     <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A129" s="1"/>
       <c r="B129" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>53</v>
       </c>
+      <c r="H129" s="1"/>
       <c r="I129" s="1" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B130" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C130" s="6" t="s">
+      <c r="A130" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C130" s="1"/>
+      <c r="I130" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:10" ht="27" customHeight="1">
+      <c r="B132" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I130" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A131" s="5" t="s">
+      <c r="I132" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C131" s="1"/>
-      <c r="I131" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A132" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A133" s="1"/>
-      <c r="B133" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I133" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A134" s="1"/>
-      <c r="B134" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I134" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="J134" s="1"/>
+      <c r="B133" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I134" s="1"/>
     </row>
     <row r="135" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A135" s="1"/>
       <c r="B135" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I135" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="J135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B136" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I136" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="27" customHeight="1">
-      <c r="A137" s="1"/>
-      <c r="B137" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I137" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A138" s="1"/>
-      <c r="B138" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I138" s="11" t="s">
-        <v>151</v>
-      </c>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A136" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C138" s="1"/>
+      <c r="I138" s="1"/>
     </row>
     <row r="139" spans="1:10" ht="13.5" customHeight="1">
       <c r="B139" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C139" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B140" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C141" s="1"/>
+      <c r="I141" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I139" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B140" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C140" s="6" t="s">
+      <c r="I143" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A144" s="1"/>
+      <c r="B144" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I140" s="9" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B141" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I141" s="9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A142" s="1"/>
-      <c r="B142" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="I142" s="9" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A143" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I143" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="J143" s="1"/>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A144" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="I144" s="1"/>
-    </row>
-    <row r="145" spans="1:9" ht="30" customHeight="1">
+      <c r="I144" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="J144" s="1"/>
+    </row>
+    <row r="145" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A145" s="1"/>
       <c r="B145" s="6" t="s">
         <v>28</v>
       </c>
@@ -2688,139 +2703,262 @@
         <v>29</v>
       </c>
       <c r="I145" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="30" customHeight="1">
+        <v>148</v>
+      </c>
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:10" ht="28.8" customHeight="1">
       <c r="B146" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I146" s="9"/>
-    </row>
-    <row r="147" spans="1:9" ht="30.6" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="I146" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="27" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I147" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A148" s="1"/>
+      <c r="B148" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I148" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C149" s="6"/>
+      <c r="I149" s="11"/>
+    </row>
+    <row r="150" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B150" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B151" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B152" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A153" s="1"/>
+      <c r="B153" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A154" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J154" s="1"/>
+    </row>
+    <row r="155" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A155" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:10" ht="30" customHeight="1">
+      <c r="B156" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="30" customHeight="1">
+      <c r="B157" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I157" s="9"/>
+    </row>
+    <row r="158" spans="1:10" ht="30" customHeight="1">
+      <c r="A158" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C158" s="6"/>
+      <c r="I158" s="9"/>
+    </row>
+    <row r="159" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A159" s="1"/>
+      <c r="B159" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I147" s="11" t="s">
+      <c r="I159" s="11" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A148" s="6" t="s">
+    <row r="160" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A160" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B160" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="I148" s="11"/>
-    </row>
-    <row r="149" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A149" s="1"/>
-      <c r="B149" s="6" t="s">
+      <c r="I160" s="11"/>
+    </row>
+    <row r="161" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A161" s="1"/>
+      <c r="B161" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I149" s="11" t="s">
+      <c r="I161" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B150" s="6" t="s">
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B162" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I150" s="11" t="s">
+      <c r="I162" s="11" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A151" s="1"/>
-      <c r="I151" s="11" t="s">
+    <row r="163" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A163" s="1"/>
+      <c r="I163" s="11" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A152" s="1"/>
-      <c r="I152" s="11" t="s">
+    <row r="164" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A164" s="1"/>
+      <c r="I164" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="9" t="s">
+    <row r="165" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A165" s="1"/>
+      <c r="B165" s="1"/>
+      <c r="H165" s="1"/>
+      <c r="I165" s="9" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A154" s="1"/>
-      <c r="H154" s="1"/>
-      <c r="I154" s="9" t="s">
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A166" s="1"/>
+      <c r="H166" s="1"/>
+      <c r="I166" s="9" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="28.2" customHeight="1">
-      <c r="I155" s="9" t="s">
+    <row r="167" spans="1:9" ht="28.2" customHeight="1">
+      <c r="I167" s="9" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A156" s="7" t="s">
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A168" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B168" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G156">
+      <c r="G168">
         <v>1</v>
       </c>
-      <c r="I156" s="1"/>
-    </row>
-    <row r="157" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A157" s="5" t="s">
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A169" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B157" s="7"/>
-      <c r="I157" s="1"/>
-    </row>
-    <row r="158" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A158" s="6" t="s">
+      <c r="B169" s="7"/>
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A170" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B170" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I158" s="1"/>
-    </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I159" s="1"/>
-    </row>
-    <row r="160" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I160" s="1"/>
-    </row>
-    <row r="161" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I161" s="1"/>
-    </row>
-    <row r="162" spans="9:9" ht="13.5" customHeight="1">
-      <c r="I162" s="1"/>
-    </row>
-    <row r="163" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="164" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="165" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="166" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="167" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="168" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="169" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="170" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="171" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="172" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="173" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="174" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="175" spans="9:9" ht="13.5" customHeight="1"/>
-    <row r="176" spans="9:9" ht="13.5" customHeight="1"/>
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A171" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="I171" s="1"/>
+    </row>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I173" s="1"/>
+    </row>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I174" s="1"/>
+    </row>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -2853,45 +2991,45 @@
     <row r="206" ht="13.5" customHeight="1"/>
     <row r="207" ht="13.5" customHeight="1"/>
     <row r="208" ht="13.5" customHeight="1"/>
-    <row r="209" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="210" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="211" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="212" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="213" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="214" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="215" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="216" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="217" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="218" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="219" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A219" s="1" t="s">
+    <row r="209" ht="13.5" customHeight="1"/>
+    <row r="210" ht="13.5" customHeight="1"/>
+    <row r="211" ht="13.5" customHeight="1"/>
+    <row r="212" ht="13.5" customHeight="1"/>
+    <row r="213" ht="13.5" customHeight="1"/>
+    <row r="214" ht="13.5" customHeight="1"/>
+    <row r="215" ht="13.5" customHeight="1"/>
+    <row r="216" ht="13.5" customHeight="1"/>
+    <row r="217" ht="13.5" customHeight="1"/>
+    <row r="218" ht="13.5" customHeight="1"/>
+    <row r="219" ht="13.5" customHeight="1"/>
+    <row r="220" ht="13.5" customHeight="1"/>
+    <row r="221" ht="13.5" customHeight="1"/>
+    <row r="222" ht="13.5" customHeight="1"/>
+    <row r="223" ht="13.5" customHeight="1"/>
+    <row r="224" ht="13.5" customHeight="1"/>
+    <row r="225" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="226" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="227" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="228" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="229" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="230" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="231" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A231" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B219" s="1" t="s">
+      <c r="B231" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="221" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="222" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="223" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="224" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="225" ht="13.5" customHeight="1"/>
-    <row r="226" ht="13.5" customHeight="1"/>
-    <row r="227" ht="13.5" customHeight="1"/>
-    <row r="228" ht="13.5" customHeight="1"/>
-    <row r="229" ht="13.5" customHeight="1"/>
-    <row r="230" ht="13.5" customHeight="1"/>
-    <row r="231" ht="13.5" customHeight="1"/>
-    <row r="232" ht="13.5" customHeight="1"/>
-    <row r="233" ht="13.5" customHeight="1"/>
-    <row r="234" ht="13.5" customHeight="1"/>
-    <row r="235" ht="13.5" customHeight="1"/>
-    <row r="236" ht="13.5" customHeight="1"/>
-    <row r="237" ht="13.5" customHeight="1"/>
-    <row r="238" ht="13.5" customHeight="1"/>
-    <row r="239" ht="13.5" customHeight="1"/>
-    <row r="240" ht="13.5" customHeight="1"/>
+    <row r="232" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="233" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="234" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="235" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="236" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="237" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="238" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="239" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="240" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="241" ht="13.5" customHeight="1"/>
     <row r="242" ht="13.5" customHeight="1"/>
     <row r="243" ht="13.5" customHeight="1"/>
@@ -3733,6 +3871,18 @@
     <row r="1079" ht="13.5" customHeight="1"/>
     <row r="1080" ht="13.5" customHeight="1"/>
     <row r="1081" ht="13.5" customHeight="1"/>
+    <row r="1082" ht="13.5" customHeight="1"/>
+    <row r="1083" ht="13.5" customHeight="1"/>
+    <row r="1084" ht="13.5" customHeight="1"/>
+    <row r="1085" ht="13.5" customHeight="1"/>
+    <row r="1086" ht="13.5" customHeight="1"/>
+    <row r="1087" ht="13.5" customHeight="1"/>
+    <row r="1088" ht="13.5" customHeight="1"/>
+    <row r="1089" ht="13.5" customHeight="1"/>
+    <row r="1090" ht="13.5" customHeight="1"/>
+    <row r="1091" ht="13.5" customHeight="1"/>
+    <row r="1092" ht="13.5" customHeight="1"/>
+    <row r="1093" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
